--- a/data_analysis/analysis_of_success_factors.xlsx
+++ b/data_analysis/analysis_of_success_factors.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Dafny\TESTDAFNY110\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADFAEA6-6669-480E-8E1D-327389BB9503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD890DD9-667D-46E4-8D17-1979D9584ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2433,7 +2433,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="12">
         <v>26</v>
